--- a/sheets/민요/검수/상주 모심기.xlsx
+++ b/sheets/민요/검수/상주 모심기.xlsx
@@ -4,14 +4,14 @@
   <sheets>
     <sheet name="정보" sheetId="1" r:id="rId1"/>
     <sheet name="정간목록" sheetId="2" r:id="rId2"/>
-    <sheet name="악보 1" sheetId="3" r:id="rId3"/>
+    <sheet name="악보" sheetId="3" r:id="rId3"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <name val="맑은 고딕"/>
@@ -20,6 +20,26 @@
     <font>
       <b/>
       <sz val="11"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="맑은 고딕"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="맑은 고딕"/>
+    </font>
+    <font>
+      <sz val="22"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="13"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
     </font>
@@ -50,7 +70,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -73,11 +93,71 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFFFFFFF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFFFFFFF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFFFFFFF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFFFFFFF"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -96,6 +176,63 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2421,8 +2558,12 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <pageSetUpPr fitToPage="0"/>
+  </sheetPr>
+  <dimension ref="A1:Q14"/>
   <cols>
-    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="1" max="1" width="2" customWidth="1"/>
     <col min="2" max="2" width="9" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
     <col min="4" max="4" width="9" customWidth="1"/>
@@ -2441,662 +2582,601 @@
     <col min="17" max="17" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">상주 모심기 — 민요채보-1/상주 모심기.png</t>
-        </is>
-      </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
-      <c r="J1" s="6"/>
-      <c r="K1" s="6"/>
-      <c r="L1" s="6"/>
-      <c r="M1" s="6"/>
-      <c r="N1" s="6"/>
-      <c r="O1" s="6"/>
-      <c r="P1" s="6"/>
-      <c r="Q1" s="6"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">정간</t>
-        </is>
-      </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8줄</t>
-        </is>
-      </c>
-      <c r="C2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="D2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7줄</t>
-        </is>
-      </c>
-      <c r="E2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="F2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6줄</t>
-        </is>
-      </c>
-      <c r="G2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="H2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5줄</t>
-        </is>
-      </c>
-      <c r="I2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="J2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4줄</t>
-        </is>
-      </c>
-      <c r="K2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="L2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3줄</t>
-        </is>
-      </c>
-      <c r="M2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="N2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2줄</t>
-        </is>
-      </c>
-      <c r="O2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="P2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1줄</t>
-        </is>
-      </c>
-      <c r="Q2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="1">
-        <v>1</v>
-      </c>
-      <c r="B3" s="5" t="inlineStr">
+    <row r="1"/>
+    <row r="2" ht="60" customHeight="1">
+      <c s="8" t="inlineStr" r="B2">
+        <is>
+          <t xml:space="preserve">상주 모심기</t>
+        </is>
+      </c>
+      <c s="8" r="C2"/>
+      <c s="8" r="D2"/>
+      <c s="8" r="E2"/>
+      <c s="8" r="F2"/>
+      <c s="8" r="G2"/>
+      <c s="8" r="H2"/>
+      <c s="8" r="I2"/>
+      <c s="8" r="J2"/>
+      <c s="8" r="K2"/>
+      <c s="8" r="L2"/>
+      <c s="8" r="M2"/>
+      <c s="8" r="N2"/>
+      <c s="8" r="O2"/>
+      <c s="8" r="P2"/>
+      <c s="8" r="Q2"/>
+    </row>
+    <row r="3" ht="56" customHeight="1">
+      <c r="B3" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">?</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
       </c>
-      <c r="D3" s="5" t="inlineStr">
+      <c r="D3" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">?</t>
         </is>
       </c>
-      <c r="E3" s="5" t="inlineStr">
+      <c r="E3" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">우리</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="F3" s="17" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="G3" s="20"/>
+      <c r="H3" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="I3" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">따</t>
         </is>
       </c>
-      <c r="J3" s="5" t="inlineStr">
+      <c r="J3" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">?</t>
         </is>
       </c>
-      <c r="K3" s="5" t="inlineStr">
+      <c r="K3" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">여밥</t>
         </is>
       </c>
-      <c r="L3" s="2" t="inlineStr">
+      <c r="L3" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">無無</t>
         </is>
       </c>
-      <c r="M3" s="2" t="inlineStr">
+      <c r="M3" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">뭇에</t>
         </is>
       </c>
-      <c r="N3" s="2" t="inlineStr">
+      <c r="N3" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">無無</t>
         </is>
       </c>
-      <c r="O3" s="2" t="inlineStr">
+      <c r="O3" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">공갈</t>
         </is>
       </c>
-      <c r="P3" s="2" t="inlineStr">
+      <c r="P3" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="Q3" s="2" t="inlineStr">
+      <c r="Q3" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">상</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="32" customHeight="1">
-      <c r="A4" s="1">
-        <v>2</v>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
+    <row r="4" ht="56" customHeight="1">
+      <c r="B4" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="C4" s="21"/>
+      <c r="D4" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="E4" s="21"/>
+      <c r="F4" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="G4" s="21"/>
+      <c r="H4" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="I4" s="2"/>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="I4" s="21"/>
+      <c r="J4" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="K4" s="2"/>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="K4" s="21"/>
+      <c r="L4" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="M4" s="2"/>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="M4" s="21"/>
+      <c r="N4" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="O4" s="2"/>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+      <c r="O4" s="21"/>
+      <c r="P4" s="17" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 仲</t>
-        </is>
-      </c>
-      <c r="Q4" s="2"/>
-    </row>
-    <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="1">
-        <v>3</v>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="Q4" s="21"/>
+    </row>
+    <row r="5" ht="56" customHeight="1">
+      <c r="B5" s="17" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="C5" s="22"/>
+      <c r="D5" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E5" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">부</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F5" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">無南仲</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G5" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">바앙</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="H5" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">太潢</t>
         </is>
       </c>
-      <c r="I5" s="3" t="inlineStr">
+      <c r="I5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">줄바아</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="J5" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="K5" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">따</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr">
+      <c r="L5" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="M5" s="2"/>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="O5" s="2"/>
-      <c r="P5" s="2" t="inlineStr">
+      <c r="M5" s="22"/>
+      <c r="N5" s="17" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="O5" s="22"/>
+      <c r="P5" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="Q5" s="2"/>
-    </row>
-    <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="1">
-        <v>4</v>
-      </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2"/>
-      <c r="I6" s="2"/>
-      <c r="J6" s="2"/>
-      <c r="K6" s="2"/>
-      <c r="L6" s="2"/>
-      <c r="M6" s="2"/>
-      <c r="N6" s="2"/>
-      <c r="O6" s="2"/>
-      <c r="P6" s="2"/>
-      <c r="Q6" s="2"/>
-    </row>
-    <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="1">
-        <v>5</v>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="Q5" s="22"/>
+    </row>
+    <row r="6" ht="56" customHeight="1">
+      <c r="B6" s="17"/>
+      <c r="C6" s="20"/>
+      <c r="D6" s="17"/>
+      <c r="E6" s="20"/>
+      <c r="F6" s="17"/>
+      <c r="G6" s="20"/>
+      <c r="H6" s="17"/>
+      <c r="I6" s="20"/>
+      <c r="J6" s="17"/>
+      <c r="K6" s="20"/>
+      <c r="L6" s="17"/>
+      <c r="M6" s="20"/>
+      <c r="N6" s="17"/>
+      <c r="O6" s="20"/>
+      <c r="P6" s="17"/>
+      <c r="Q6" s="20"/>
+    </row>
+    <row r="7" ht="56" customHeight="1">
+      <c r="B7" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">모</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="D7" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">?</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr">
+      <c r="E7" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">내파아</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="F7" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">?</t>
         </is>
       </c>
-      <c r="G7" s="5" t="inlineStr">
+      <c r="G7" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">주우</t>
         </is>
       </c>
-      <c r="H7" s="5" t="inlineStr">
+      <c r="H7" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">?</t>
         </is>
       </c>
-      <c r="I7" s="5" t="inlineStr">
+      <c r="I7" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">저어</t>
         </is>
       </c>
-      <c r="J7" s="3" t="inlineStr">
+      <c r="J7" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">無汰</t>
         </is>
       </c>
-      <c r="K7" s="3" t="inlineStr">
+      <c r="K7" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">자아야</t>
         </is>
       </c>
-      <c r="L7" s="3" t="inlineStr">
+      <c r="L7" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">無汰</t>
         </is>
       </c>
-      <c r="M7" s="3" t="inlineStr">
+      <c r="M7" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">저어</t>
         </is>
       </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="N7" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="O7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">재</t>
         </is>
       </c>
-      <c r="P7" s="3" t="inlineStr">
+      <c r="P7" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">無汰</t>
         </is>
       </c>
-      <c r="Q7" s="3" t="inlineStr">
+      <c r="Q7" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">주</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="1">
-        <v>6</v>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
+    <row r="8" ht="56" customHeight="1">
+      <c r="B8" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">南無南</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C8" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">다아</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D8" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E8" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">주우</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F8" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">仲姑</t>
         </is>
       </c>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="G8" s="22"/>
+      <c r="H8" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">南無仲</t>
         </is>
       </c>
-      <c r="I8" s="2"/>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="I8" s="22"/>
+      <c r="J8" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="K8" s="2"/>
-      <c r="L8" s="2" t="inlineStr">
+      <c r="K8" s="22"/>
+      <c r="L8" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">仲姑</t>
         </is>
       </c>
-      <c r="M8" s="2"/>
-      <c r="N8" s="2" t="inlineStr">
+      <c r="M8" s="22"/>
+      <c r="N8" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="O8" s="2"/>
-      <c r="P8" s="3" t="inlineStr">
+      <c r="O8" s="22"/>
+      <c r="P8" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">汰潢汰</t>
         </is>
       </c>
-      <c r="Q8" s="3"/>
-    </row>
-    <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="1">
-        <v>7</v>
-      </c>
-      <c r="B9" s="2"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="Q8" s="23"/>
+    </row>
+    <row r="9" ht="56" customHeight="1">
+      <c r="B9" s="17"/>
+      <c r="C9" s="20"/>
+      <c r="D9" s="17"/>
+      <c r="E9" s="20"/>
+      <c r="F9" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="G9" s="2"/>
-      <c r="H9" s="2"/>
-      <c r="I9" s="2"/>
-      <c r="J9" s="2"/>
-      <c r="K9" s="2"/>
-      <c r="L9" s="2" t="inlineStr">
+      <c r="G9" s="20"/>
+      <c r="H9" s="17"/>
+      <c r="I9" s="20"/>
+      <c r="J9" s="17"/>
+      <c r="K9" s="20"/>
+      <c r="L9" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="M9" s="2"/>
-      <c r="N9" s="2" t="inlineStr">
+      <c r="M9" s="20"/>
+      <c r="N9" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">仲姑</t>
         </is>
       </c>
-      <c r="O9" s="2"/>
-      <c r="P9" s="2"/>
-      <c r="Q9" s="2"/>
-    </row>
-    <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="1">
-        <v>8</v>
-      </c>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
-      <c r="I10" s="2"/>
-      <c r="J10" s="2"/>
-      <c r="K10" s="2"/>
-      <c r="L10" s="2"/>
-      <c r="M10" s="2"/>
-      <c r="N10" s="2"/>
-      <c r="O10" s="2"/>
-      <c r="P10" s="2"/>
-      <c r="Q10" s="2"/>
-    </row>
-    <row r="11" ht="32" customHeight="1">
-      <c r="A11" s="1">
-        <v>9</v>
-      </c>
-      <c r="B11" s="2"/>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="O9" s="20"/>
+      <c r="P9" s="17"/>
+      <c r="Q9" s="20"/>
+    </row>
+    <row r="10" ht="56" customHeight="1">
+      <c r="B10" s="17"/>
+      <c r="C10" s="21"/>
+      <c r="D10" s="17"/>
+      <c r="E10" s="21"/>
+      <c r="F10" s="17"/>
+      <c r="G10" s="21"/>
+      <c r="H10" s="17"/>
+      <c r="I10" s="21"/>
+      <c r="J10" s="17"/>
+      <c r="K10" s="21"/>
+      <c r="L10" s="17"/>
+      <c r="M10" s="21"/>
+      <c r="N10" s="17"/>
+      <c r="O10" s="21"/>
+      <c r="P10" s="17"/>
+      <c r="Q10" s="21"/>
+    </row>
+    <row r="11" ht="56" customHeight="1">
+      <c r="B11" s="17"/>
+      <c r="C11" s="22"/>
+      <c r="D11" s="17"/>
+      <c r="E11" s="22"/>
+      <c r="F11" s="17"/>
+      <c r="G11" s="22"/>
+      <c r="H11" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="I11" s="2"/>
-      <c r="J11" s="2" t="inlineStr">
+      <c r="I11" s="22"/>
+      <c r="J11" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="K11" s="2"/>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+      <c r="K11" s="22"/>
+      <c r="L11" s="17" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 △</t>
-        </is>
-      </c>
-      <c r="M11" s="2"/>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="O11" s="2"/>
-      <c r="P11" s="2" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="M11" s="22"/>
+      <c r="N11" s="17" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="O11" s="22"/>
+      <c r="P11" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="Q11" s="2"/>
-    </row>
-    <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="1">
-        <v>10</v>
-      </c>
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2"/>
-      <c r="I12" s="2"/>
-      <c r="J12" s="2"/>
-      <c r="K12" s="2"/>
-      <c r="L12" s="2"/>
-      <c r="M12" s="2"/>
-      <c r="N12" s="2"/>
-      <c r="O12" s="2"/>
-      <c r="P12" s="2"/>
-      <c r="Q12" s="2"/>
-    </row>
-    <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="1">
-        <v>11</v>
-      </c>
-      <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2"/>
-      <c r="I13" s="2"/>
-      <c r="J13" s="2"/>
-      <c r="K13" s="2"/>
-      <c r="L13" s="2"/>
-      <c r="M13" s="2"/>
-      <c r="N13" s="2" t="inlineStr">
+      <c r="Q11" s="22"/>
+    </row>
+    <row r="12" ht="56" customHeight="1">
+      <c r="B12" s="17"/>
+      <c r="C12" s="20"/>
+      <c r="D12" s="17"/>
+      <c r="E12" s="20"/>
+      <c r="F12" s="17"/>
+      <c r="G12" s="20"/>
+      <c r="H12" s="17"/>
+      <c r="I12" s="20"/>
+      <c r="J12" s="17"/>
+      <c r="K12" s="20"/>
+      <c r="L12" s="17"/>
+      <c r="M12" s="20"/>
+      <c r="N12" s="17"/>
+      <c r="O12" s="20"/>
+      <c r="P12" s="17"/>
+      <c r="Q12" s="20"/>
+    </row>
+    <row r="13" ht="56" customHeight="1">
+      <c r="B13" s="17"/>
+      <c r="C13" s="21"/>
+      <c r="D13" s="17"/>
+      <c r="E13" s="21"/>
+      <c r="F13" s="17"/>
+      <c r="G13" s="21"/>
+      <c r="H13" s="17"/>
+      <c r="I13" s="21"/>
+      <c r="J13" s="17"/>
+      <c r="K13" s="21"/>
+      <c r="L13" s="17"/>
+      <c r="M13" s="21"/>
+      <c r="N13" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="O13" s="2"/>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="Q13" s="2"/>
-    </row>
-    <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="1">
-        <v>12</v>
-      </c>
-      <c r="B14" s="2"/>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2"/>
-      <c r="I14" s="2"/>
-      <c r="J14" s="2"/>
-      <c r="K14" s="2"/>
-      <c r="L14" s="2"/>
-      <c r="M14" s="2"/>
-      <c r="N14" s="3" t="inlineStr">
+      <c r="O13" s="21"/>
+      <c r="P13" s="17" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="Q13" s="21"/>
+    </row>
+    <row r="14" ht="56" customHeight="1">
+      <c r="B14" s="17"/>
+      <c r="C14" s="22"/>
+      <c r="D14" s="17"/>
+      <c r="E14" s="22"/>
+      <c r="F14" s="17"/>
+      <c r="G14" s="22"/>
+      <c r="H14" s="17"/>
+      <c r="I14" s="22"/>
+      <c r="J14" s="17"/>
+      <c r="K14" s="22"/>
+      <c r="L14" s="17"/>
+      <c r="M14" s="22"/>
+      <c r="N14" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">太汰</t>
         </is>
       </c>
-      <c r="O14" s="3"/>
-      <c r="P14" s="3" t="inlineStr">
+      <c r="O14" s="23"/>
+      <c r="P14" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">太姑汰</t>
         </is>
       </c>
-      <c r="Q14" s="3"/>
+      <c r="Q14" s="23"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B2:Q2"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" fitToWidth="1" fitToHeight="0" scale="76"/>
 </worksheet>
 </file>
--- a/sheets/민요/검수/상주 모심기.xlsx
+++ b/sheets/민요/검수/상주 모심기.xlsx
@@ -409,7 +409,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">― 연음 · △ 쉼 · 점 · ○ 동그라미 · ⁚ 두 점 · ‹ 정간 경계 표시 · ／ 사선 (· ○ ⁚ ‹ ／ 는 화면 표시 전용)</t>
+          <t xml:space="preserve">– 연음 · △ 쉼 · 점 · ○ 동그라미 · ⁚ 두 점 · ‹ 정간 경계 표시 · ／ 사선 (· ○ ⁚ ‹ ／ 는 화면 표시 전용)</t>
         </is>
       </c>
     </row>
@@ -549,13 +549,13 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無|―|南</t>
+          <t xml:space="preserve">無|–|南</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">無
-―
+–
 南</t>
         </is>
       </c>
@@ -629,12 +629,12 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|‹</t>
+          <t xml:space="preserve">–|‹</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 ‹</t>
         </is>
       </c>
@@ -665,13 +665,13 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無|―|南</t>
+          <t xml:space="preserve">無|–|南</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">無
-―
+–
 南</t>
         </is>
       </c>
@@ -745,12 +745,12 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|△</t>
+          <t xml:space="preserve">–|△</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 △</t>
         </is>
       </c>
@@ -940,12 +940,12 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|△|‹</t>
+          <t xml:space="preserve">–|△|‹</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 △
 ‹</t>
         </is>
@@ -1018,14 +1018,14 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無|無^|―</t>
+          <t xml:space="preserve">無|無^|–</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 無^
-―</t>
+–</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1059,12 +1059,12 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I15" s="2"/>
@@ -1094,12 +1094,12 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|南</t>
+          <t xml:space="preserve">–|南</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 南</t>
         </is>
       </c>
@@ -1173,12 +1173,12 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I18" s="2"/>
@@ -1327,13 +1327,13 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲|―|姑</t>
+          <t xml:space="preserve">仲|–|姑</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
-―
+–
 姑</t>
         </is>
       </c>
@@ -1407,12 +1407,12 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I24" s="2"/>
@@ -1442,12 +1442,12 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|○</t>
+          <t xml:space="preserve">–|○</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 ○</t>
         </is>
       </c>
@@ -1682,12 +1682,12 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|△</t>
+          <t xml:space="preserve">–|△</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 △</t>
         </is>
       </c>
@@ -1893,12 +1893,12 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I36" s="2"/>
@@ -1965,14 +1965,14 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無|無^|―</t>
+          <t xml:space="preserve">無|無^|–</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 無^
-―</t>
+–</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2006,12 +2006,12 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|南</t>
+          <t xml:space="preserve">–|南</t>
         </is>
       </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 南</t>
         </is>
       </c>
@@ -2046,12 +2046,12 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|南</t>
+          <t xml:space="preserve">–|南</t>
         </is>
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 南</t>
         </is>
       </c>
@@ -2062,7 +2062,7 @@
       </c>
       <c r="J40" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">정정 종이 위, 위쪽 ― 획이 亻일 수도(㑲?)</t>
+          <t xml:space="preserve">정정 종이 위, 위쪽 – 획이 亻일 수도(㑲?)</t>
         </is>
       </c>
       <c r="K40" s="2"/>
@@ -2129,12 +2129,12 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I42" s="2"/>
@@ -2283,13 +2283,13 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲|―|姑</t>
+          <t xml:space="preserve">仲|–|姑</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
-―
+–
 姑</t>
         </is>
       </c>
@@ -2363,12 +2363,12 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I48" s="2"/>
@@ -2458,7 +2458,7 @@
         <is>
           <t xml:space="preserve">無
 無^
-―</t>
+–</t>
         </is>
       </c>
       <c r="C3" s="8" t="inlineStr">
@@ -2480,7 +2480,7 @@
         <is>
           <t xml:space="preserve">無
 無^
-―</t>
+–</t>
         </is>
       </c>
       <c r="G3" s="8" t="inlineStr">
@@ -2491,7 +2491,7 @@
       <c r="H3" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">無
-―
+–
 南</t>
         </is>
       </c>
@@ -2505,7 +2505,7 @@
       <c r="A4" s="0"/>
       <c r="B4" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 南</t>
         </is>
       </c>
@@ -2522,7 +2522,7 @@
       </c>
       <c r="F4" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="G4" s="9"/>
@@ -2541,7 +2541,7 @@
       <c r="A5" s="0"/>
       <c r="B5" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 南</t>
         </is>
       </c>
@@ -2562,7 +2562,7 @@
       </c>
       <c r="F5" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 南</t>
         </is>
       </c>
@@ -2573,7 +2573,7 @@
       </c>
       <c r="H5" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 ‹</t>
         </is>
       </c>
@@ -2614,7 +2614,7 @@
       <c r="H6" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">無
-―
+–
 南</t>
         </is>
       </c>
@@ -2628,7 +2628,7 @@
       <c r="A7" s="0"/>
       <c r="B7" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="C7" s="9"/>
@@ -2645,7 +2645,7 @@
       </c>
       <c r="F7" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="G7" s="9"/>
@@ -2674,7 +2674,7 @@
       </c>
       <c r="D8" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 △</t>
         </is>
       </c>
@@ -2691,7 +2691,7 @@
       </c>
       <c r="H8" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 △</t>
         </is>
       </c>
@@ -2794,7 +2794,7 @@
       <c r="B11" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
-―
+–
 姑</t>
         </is>
       </c>
@@ -2818,7 +2818,7 @@
       <c r="F11" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
-―
+–
 姑</t>
         </is>
       </c>
@@ -2887,25 +2887,25 @@
       <c r="A13" s="0"/>
       <c r="B13" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="C13" s="9"/>
       <c r="D13" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="E13" s="9"/>
       <c r="F13" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="G13" s="9"/>
       <c r="H13" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 △
 ‹</t>
         </is>
@@ -2931,7 +2931,7 @@
       <c r="E14" s="10"/>
       <c r="F14" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 ○</t>
         </is>
       </c>

--- a/sheets/민요/검수/상주 모심기.xlsx
+++ b/sheets/민요/검수/상주 모심기.xlsx
@@ -11,27 +11,43 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="4">
+  <fonts count="7">
     <font>
       <sz val="11"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="22"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="24"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="24"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -134,7 +150,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -157,7 +173,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <!-- 8~16: 박 묶음 가사 칸 = (일반 8~10 · 비고 11~13 · 팔레트 외 14~16) × (첫 · 가운데 · 마지막) -->
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -185,7 +200,6 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <!-- 17~19: 악보 율명 칸 22pt (가사 11pt 의 두 배) = 일반 · 비고 · 팔레트 외 -->
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -193,6 +207,33 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2439,63 +2480,63 @@
     </row>
     <row r="2" ht="60" customHeight="1">
       <c r="A2" s="0"/>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">상주 모심기</t>
         </is>
       </c>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
+      <c r="I2" s="20"/>
     </row>
     <row r="3" ht="56" customHeight="1">
       <c r="A3" s="0"/>
-      <c r="B3" s="17" t="inlineStr">
+      <c r="B3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 無^
 –</t>
         </is>
       </c>
-      <c r="C3" s="8" t="inlineStr">
+      <c r="C3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">우리</t>
         </is>
       </c>
-      <c r="D3" s="17" t="inlineStr">
+      <c r="D3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="E3" s="8" t="inlineStr">
+      <c r="E3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">여</t>
         </is>
       </c>
-      <c r="F3" s="17" t="inlineStr">
+      <c r="F3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 無^
 –</t>
         </is>
       </c>
-      <c r="G3" s="8" t="inlineStr">
+      <c r="G3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">여밥</t>
         </is>
       </c>
-      <c r="H3" s="17" t="inlineStr">
+      <c r="H3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 –
 南</t>
         </is>
       </c>
-      <c r="I3" s="8" t="inlineStr">
+      <c r="I3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">상</t>
         </is>
@@ -2503,35 +2544,35 @@
     </row>
     <row r="4" ht="56" customHeight="1">
       <c r="A4" s="0"/>
-      <c r="B4" s="18" t="inlineStr">
+      <c r="B4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 南</t>
         </is>
       </c>
-      <c r="C4" s="12"/>
-      <c r="D4" s="17" t="inlineStr">
+      <c r="C4" s="24"/>
+      <c r="D4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="E4" s="9" t="inlineStr">
+      <c r="E4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">연</t>
         </is>
       </c>
-      <c r="F4" s="17" t="inlineStr">
+      <c r="F4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="G4" s="9"/>
-      <c r="H4" s="17" t="inlineStr">
+      <c r="G4" s="25"/>
+      <c r="H4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="I4" s="9" t="inlineStr">
+      <c r="I4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">주</t>
         </is>
@@ -2539,86 +2580,86 @@
     </row>
     <row r="5" ht="56" customHeight="1">
       <c r="A5" s="0"/>
-      <c r="B5" s="18" t="inlineStr">
+      <c r="B5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 南</t>
         </is>
       </c>
-      <c r="C5" s="13" t="inlineStr">
+      <c r="C5" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
       </c>
-      <c r="D5" s="18" t="inlineStr">
+      <c r="D5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="E5" s="13" t="inlineStr">
+      <c r="E5" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">밥</t>
         </is>
       </c>
-      <c r="F5" s="17" t="inlineStr">
+      <c r="F5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 南</t>
         </is>
       </c>
-      <c r="G5" s="10" t="inlineStr">
+      <c r="G5" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">압</t>
         </is>
       </c>
-      <c r="H5" s="17" t="inlineStr">
+      <c r="H5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 ‹</t>
         </is>
       </c>
-      <c r="I5" s="10"/>
+      <c r="I5" s="27"/>
     </row>
     <row r="6" ht="56" customHeight="1">
       <c r="A6" s="0"/>
-      <c r="B6" s="17" t="inlineStr">
+      <c r="B6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">부</t>
         </is>
       </c>
-      <c r="D6" s="17" t="inlineStr">
+      <c r="D6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰^</t>
         </is>
       </c>
-      <c r="E6" s="8" t="inlineStr">
+      <c r="E6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">줄</t>
         </is>
       </c>
-      <c r="F6" s="17" t="inlineStr">
+      <c r="F6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="G6" s="8" t="inlineStr">
+      <c r="G6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">따</t>
         </is>
       </c>
-      <c r="H6" s="17" t="inlineStr">
+      <c r="H6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 –
 南</t>
         </is>
       </c>
-      <c r="I6" s="8" t="inlineStr">
+      <c r="I6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">함</t>
         </is>
@@ -2626,35 +2667,35 @@
     </row>
     <row r="7" ht="56" customHeight="1">
       <c r="A7" s="0"/>
-      <c r="B7" s="17" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C7" s="9"/>
-      <c r="D7" s="17" t="inlineStr">
+      <c r="C7" s="25"/>
+      <c r="D7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無南
 仲</t>
         </is>
       </c>
-      <c r="E7" s="9" t="inlineStr">
+      <c r="E7" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">바압</t>
         </is>
       </c>
-      <c r="F7" s="17" t="inlineStr">
+      <c r="F7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="G7" s="9"/>
-      <c r="H7" s="17" t="inlineStr">
+      <c r="G7" s="25"/>
+      <c r="H7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="I7" s="9" t="inlineStr">
+      <c r="I7" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">창</t>
         </is>
@@ -2662,79 +2703,79 @@
     </row>
     <row r="8" ht="56" customHeight="1">
       <c r="A8" s="0"/>
-      <c r="B8" s="17" t="inlineStr">
+      <c r="B8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="C8" s="10" t="inlineStr">
+      <c r="C8" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">모</t>
         </is>
       </c>
-      <c r="D8" s="17" t="inlineStr">
+      <c r="D8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 △</t>
         </is>
       </c>
-      <c r="E8" s="10"/>
-      <c r="F8" s="17" t="inlineStr">
+      <c r="E8" s="27"/>
+      <c r="F8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="G8" s="10" t="inlineStr">
+      <c r="G8" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">는</t>
         </is>
       </c>
-      <c r="H8" s="17" t="inlineStr">
+      <c r="H8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 △</t>
         </is>
       </c>
-      <c r="I8" s="10"/>
+      <c r="I8" s="27"/>
     </row>
     <row r="9" ht="56" customHeight="1">
       <c r="A9" s="0"/>
-      <c r="B9" s="17" t="inlineStr">
+      <c r="B9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="C9" s="8" t="inlineStr">
+      <c r="C9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">모</t>
         </is>
       </c>
-      <c r="D9" s="18" t="inlineStr">
+      <c r="D9" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="E9" s="11" t="inlineStr">
+      <c r="E9" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">내</t>
         </is>
       </c>
-      <c r="F9" s="17" t="inlineStr">
+      <c r="F9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="G9" s="8" t="inlineStr">
+      <c r="G9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">저</t>
         </is>
       </c>
-      <c r="H9" s="17" t="inlineStr">
+      <c r="H9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="I9" s="8" t="inlineStr">
+      <c r="I9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">공</t>
         </is>
@@ -2742,48 +2783,48 @@
     </row>
     <row r="10" ht="56" customHeight="1">
       <c r="A10" s="0"/>
-      <c r="B10" s="17" t="inlineStr">
+      <c r="B10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 無
 南</t>
         </is>
       </c>
-      <c r="C10" s="9" t="inlineStr">
+      <c r="C10" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">셔어</t>
         </is>
       </c>
-      <c r="D10" s="18" t="inlineStr">
+      <c r="D10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 汰</t>
         </is>
       </c>
-      <c r="E10" s="12" t="inlineStr">
+      <c r="E10" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">따아</t>
         </is>
       </c>
-      <c r="F10" s="17" t="inlineStr">
+      <c r="F10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 無
 南</t>
         </is>
       </c>
-      <c r="G10" s="9" t="inlineStr">
+      <c r="G10" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">처어</t>
         </is>
       </c>
-      <c r="H10" s="17" t="inlineStr">
+      <c r="H10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 汰</t>
         </is>
       </c>
-      <c r="I10" s="9" t="inlineStr">
+      <c r="I10" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">갈</t>
         </is>
@@ -2791,50 +2832,50 @@
     </row>
     <row r="11" ht="56" customHeight="1">
       <c r="A11" s="0"/>
-      <c r="B11" s="17" t="inlineStr">
+      <c r="B11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 –
 姑</t>
         </is>
       </c>
-      <c r="C11" s="10" t="inlineStr">
+      <c r="C11" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">다아</t>
         </is>
       </c>
-      <c r="D11" s="18" t="inlineStr">
+      <c r="D11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
 㴌
 汰</t>
         </is>
       </c>
-      <c r="E11" s="13" t="inlineStr">
+      <c r="E11" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">주우</t>
         </is>
       </c>
-      <c r="F11" s="17" t="inlineStr">
+      <c r="F11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 –
 姑</t>
         </is>
       </c>
-      <c r="G11" s="10" t="inlineStr">
+      <c r="G11" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">자아</t>
         </is>
       </c>
-      <c r="H11" s="17" t="inlineStr">
+      <c r="H11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
 㴌
 汰</t>
         </is>
       </c>
-      <c r="I11" s="10" t="inlineStr">
+      <c r="I11" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">못</t>
         </is>
@@ -2842,42 +2883,42 @@
     </row>
     <row r="12" ht="56" customHeight="1">
       <c r="A12" s="0"/>
-      <c r="B12" s="17" t="inlineStr">
+      <c r="B12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">오</t>
         </is>
       </c>
-      <c r="D12" s="18" t="inlineStr">
+      <c r="D12" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="E12" s="11" t="inlineStr">
+      <c r="E12" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">마</t>
         </is>
       </c>
-      <c r="F12" s="17" t="inlineStr">
+      <c r="F12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="G12" s="8" t="inlineStr">
+      <c r="G12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">야</t>
         </is>
       </c>
-      <c r="H12" s="17" t="inlineStr">
+      <c r="H12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="I12" s="8" t="inlineStr">
+      <c r="I12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
@@ -2885,65 +2926,65 @@
     </row>
     <row r="13" ht="56" customHeight="1">
       <c r="A13" s="0"/>
-      <c r="B13" s="17" t="inlineStr">
+      <c r="B13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C13" s="9"/>
-      <c r="D13" s="17" t="inlineStr">
+      <c r="C13" s="25"/>
+      <c r="D13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="E13" s="9"/>
-      <c r="F13" s="17" t="inlineStr">
+      <c r="E13" s="25"/>
+      <c r="F13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="G13" s="9"/>
-      <c r="H13" s="17" t="inlineStr">
+      <c r="G13" s="25"/>
+      <c r="H13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 △
 ‹</t>
         </is>
       </c>
-      <c r="I13" s="9"/>
+      <c r="I13" s="25"/>
     </row>
     <row r="14" ht="56" customHeight="1">
       <c r="A14" s="0"/>
-      <c r="B14" s="18" t="inlineStr">
+      <c r="B14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">·
 ○</t>
         </is>
       </c>
-      <c r="C14" s="13"/>
-      <c r="D14" s="17" t="inlineStr">
+      <c r="C14" s="26"/>
+      <c r="D14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
 㴌
 汰</t>
         </is>
       </c>
-      <c r="E14" s="10"/>
-      <c r="F14" s="18" t="inlineStr">
+      <c r="E14" s="27"/>
+      <c r="F14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 ○</t>
         </is>
       </c>
-      <c r="G14" s="13"/>
-      <c r="H14" s="18" t="inlineStr">
+      <c r="G14" s="26"/>
+      <c r="H14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
 㴌
 汰</t>
         </is>
       </c>
-      <c r="I14" s="13"/>
+      <c r="I14" s="26"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/sheets/민요/검수/상주 모심기.xlsx
+++ b/sheets/민요/검수/상주 모심기.xlsx
@@ -2465,20 +2465,20 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="12" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="87.31" customHeight="1">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -2493,7 +2493,7 @@
       <c r="H2" s="20"/>
       <c r="I2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="87.31" customHeight="1">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -2542,7 +2542,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="87.31" customHeight="1">
       <c r="A4" s="0"/>
       <c r="B4" s="23" t="inlineStr">
         <is>
@@ -2578,7 +2578,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="87.31" customHeight="1">
       <c r="A5" s="0"/>
       <c r="B5" s="23" t="inlineStr">
         <is>
@@ -2620,7 +2620,7 @@
       </c>
       <c r="I5" s="27"/>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="87.31" customHeight="1">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -2665,7 +2665,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="87.31" customHeight="1">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -2701,7 +2701,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="87.31" customHeight="1">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -2738,7 +2738,7 @@
       </c>
       <c r="I8" s="27"/>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="87.31" customHeight="1">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -2781,7 +2781,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="87.31" customHeight="1">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -2830,7 +2830,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="87.31" customHeight="1">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -2881,7 +2881,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="87.31" customHeight="1">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
@@ -2924,7 +2924,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="87.31" customHeight="1">
       <c r="A13" s="0"/>
       <c r="B13" s="21" t="inlineStr">
         <is>
@@ -2953,11 +2953,11 @@
       </c>
       <c r="I13" s="25"/>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="87.31" customHeight="1">
       <c r="A14" s="0"/>
       <c r="B14" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">·
+          <t xml:space="preserve">–
 ○</t>
         </is>
       </c>

--- a/sheets/민요/검수/상주 모심기.xlsx
+++ b/sheets/민요/검수/상주 모심기.xlsx
@@ -670,13 +670,12 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–|‹</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
-‹</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I4" s="2"/>
@@ -981,14 +980,13 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–|△|‹</t>
+          <t xml:space="preserve">–|△</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-△
-‹</t>
+△</t>
         </is>
       </c>
       <c r="I12" s="2"/>
@@ -2614,8 +2612,7 @@
       </c>
       <c r="H5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
-‹</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I5" s="27"/>
@@ -2947,8 +2944,7 @@
       <c r="H13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-△
-‹</t>
+△</t>
         </is>
       </c>
       <c r="I13" s="25"/>

--- a/sheets/민요/검수/상주 모심기.xlsx
+++ b/sheets/민요/검수/상주 모심기.xlsx
@@ -1481,13 +1481,12 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">–|○</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
-○</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I25" s="3"/>
@@ -2437,13 +2436,12 @@
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">·|○</t>
+          <t xml:space="preserve">·</t>
         </is>
       </c>
       <c r="H49" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">·
-○</t>
+          <t xml:space="preserve">·</t>
         </is>
       </c>
       <c r="I49" s="3"/>
@@ -2953,8 +2951,7 @@
       <c r="A14" s="0"/>
       <c r="B14" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
-○</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="C14" s="26"/>
@@ -2968,8 +2965,7 @@
       <c r="E14" s="27"/>
       <c r="F14" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
-○</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="G14" s="26"/>

--- a/sheets/민요/검수/상주 모심기.xlsx
+++ b/sheets/민요/검수/상주 모심기.xlsx
@@ -2500,7 +2500,8 @@
       </c>
       <c r="C3" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">우리</t>
+          <t xml:space="preserve">우
+리</t>
         </is>
       </c>
       <c r="D3" s="21" t="inlineStr">
@@ -2522,7 +2523,8 @@
       </c>
       <c r="G3" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">여밥</t>
+          <t xml:space="preserve">여
+밥</t>
         </is>
       </c>
       <c r="H3" s="21" t="inlineStr">
@@ -2676,7 +2678,8 @@
       </c>
       <c r="E7" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">바압</t>
+          <t xml:space="preserve">바
+압</t>
         </is>
       </c>
       <c r="F7" s="21" t="inlineStr">
@@ -2787,7 +2790,8 @@
       </c>
       <c r="C10" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">셔어</t>
+          <t xml:space="preserve">셔
+어</t>
         </is>
       </c>
       <c r="D10" s="23" t="inlineStr">
@@ -2798,7 +2802,8 @@
       </c>
       <c r="E10" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">따아</t>
+          <t xml:space="preserve">따
+아</t>
         </is>
       </c>
       <c r="F10" s="21" t="inlineStr">
@@ -2810,7 +2815,8 @@
       </c>
       <c r="G10" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">처어</t>
+          <t xml:space="preserve">처
+어</t>
         </is>
       </c>
       <c r="H10" s="21" t="inlineStr">
@@ -2836,7 +2842,8 @@
       </c>
       <c r="C11" s="27" t="inlineStr">
         <is>
-          <t xml:space="preserve">다아</t>
+          <t xml:space="preserve">다
+아</t>
         </is>
       </c>
       <c r="D11" s="23" t="inlineStr">
@@ -2848,7 +2855,8 @@
       </c>
       <c r="E11" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">주우</t>
+          <t xml:space="preserve">주
+우</t>
         </is>
       </c>
       <c r="F11" s="21" t="inlineStr">
@@ -2860,7 +2868,8 @@
       </c>
       <c r="G11" s="27" t="inlineStr">
         <is>
-          <t xml:space="preserve">자아</t>
+          <t xml:space="preserve">자
+아</t>
         </is>
       </c>
       <c r="H11" s="21" t="inlineStr">

--- a/sheets/민요/검수/상주 모심기.xlsx
+++ b/sheets/민요/검수/상주 모심기.xlsx
@@ -11,7 +11,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <name val="궁서체"/>
@@ -47,6 +47,11 @@
     </font>
     <font>
       <sz val="12"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="18"/>
       <name val="궁서체"/>
       <family val="2"/>
     </font>
@@ -150,7 +155,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -234,6 +239,24 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2498,7 +2521,7 @@
 –</t>
         </is>
       </c>
-      <c r="C3" s="22" t="inlineStr">
+      <c r="C3" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">우
 리</t>
@@ -2509,7 +2532,7 @@
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="E3" s="22" t="inlineStr">
+      <c r="E3" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">여</t>
         </is>
@@ -2521,7 +2544,7 @@
 –</t>
         </is>
       </c>
-      <c r="G3" s="22" t="inlineStr">
+      <c r="G3" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">여
 밥</t>
@@ -2534,7 +2557,7 @@
 南</t>
         </is>
       </c>
-      <c r="I3" s="22" t="inlineStr">
+      <c r="I3" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">상</t>
         </is>
@@ -2548,13 +2571,13 @@
 南</t>
         </is>
       </c>
-      <c r="C4" s="24"/>
+      <c r="C4" s="30"/>
       <c r="D4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="E4" s="25" t="inlineStr">
+      <c r="E4" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">연</t>
         </is>
@@ -2564,13 +2587,13 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="G4" s="25"/>
+      <c r="G4" s="31"/>
       <c r="H4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="I4" s="25" t="inlineStr">
+      <c r="I4" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">주</t>
         </is>
@@ -2584,7 +2607,7 @@
 南</t>
         </is>
       </c>
-      <c r="C5" s="26" t="inlineStr">
+      <c r="C5" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
@@ -2594,7 +2617,7 @@
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="E5" s="26" t="inlineStr">
+      <c r="E5" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">밥</t>
         </is>
@@ -2605,7 +2628,7 @@
 南</t>
         </is>
       </c>
-      <c r="G5" s="27" t="inlineStr">
+      <c r="G5" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">압</t>
         </is>
@@ -2615,7 +2638,7 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="I5" s="27"/>
+      <c r="I5" s="33"/>
     </row>
     <row r="6" ht="87.31" customHeight="1">
       <c r="A6" s="0"/>
@@ -2624,7 +2647,7 @@
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="C6" s="22" t="inlineStr">
+      <c r="C6" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">부</t>
         </is>
@@ -2634,7 +2657,7 @@
           <t xml:space="preserve">汰^</t>
         </is>
       </c>
-      <c r="E6" s="22" t="inlineStr">
+      <c r="E6" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">줄</t>
         </is>
@@ -2644,7 +2667,7 @@
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="G6" s="22" t="inlineStr">
+      <c r="G6" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">따</t>
         </is>
@@ -2656,7 +2679,7 @@
 南</t>
         </is>
       </c>
-      <c r="I6" s="22" t="inlineStr">
+      <c r="I6" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">함</t>
         </is>
@@ -2669,14 +2692,14 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C7" s="25"/>
+      <c r="C7" s="31"/>
       <c r="D7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無南
 仲</t>
         </is>
       </c>
-      <c r="E7" s="25" t="inlineStr">
+      <c r="E7" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">바
 압</t>
@@ -2687,13 +2710,13 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="G7" s="25"/>
+      <c r="G7" s="31"/>
       <c r="H7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="I7" s="25" t="inlineStr">
+      <c r="I7" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">창</t>
         </is>
@@ -2706,7 +2729,7 @@
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="C8" s="27" t="inlineStr">
+      <c r="C8" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">모</t>
         </is>
@@ -2717,13 +2740,13 @@
 △</t>
         </is>
       </c>
-      <c r="E8" s="27"/>
+      <c r="E8" s="33"/>
       <c r="F8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="G8" s="27" t="inlineStr">
+      <c r="G8" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">는</t>
         </is>
@@ -2734,7 +2757,7 @@
 △</t>
         </is>
       </c>
-      <c r="I8" s="27"/>
+      <c r="I8" s="33"/>
     </row>
     <row r="9" ht="87.31" customHeight="1">
       <c r="A9" s="0"/>
@@ -2743,7 +2766,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="C9" s="22" t="inlineStr">
+      <c r="C9" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">모</t>
         </is>
@@ -2753,7 +2776,7 @@
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="E9" s="28" t="inlineStr">
+      <c r="E9" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">내</t>
         </is>
@@ -2763,7 +2786,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="G9" s="22" t="inlineStr">
+      <c r="G9" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">저</t>
         </is>
@@ -2773,7 +2796,7 @@
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="I9" s="22" t="inlineStr">
+      <c r="I9" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">공</t>
         </is>
@@ -2788,7 +2811,7 @@
 南</t>
         </is>
       </c>
-      <c r="C10" s="25" t="inlineStr">
+      <c r="C10" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">셔
 어</t>
@@ -2800,7 +2823,7 @@
 汰</t>
         </is>
       </c>
-      <c r="E10" s="24" t="inlineStr">
+      <c r="E10" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">따
 아</t>
@@ -2813,7 +2836,7 @@
 南</t>
         </is>
       </c>
-      <c r="G10" s="25" t="inlineStr">
+      <c r="G10" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">처
 어</t>
@@ -2825,7 +2848,7 @@
 汰</t>
         </is>
       </c>
-      <c r="I10" s="25" t="inlineStr">
+      <c r="I10" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">갈</t>
         </is>
@@ -2840,7 +2863,7 @@
 姑</t>
         </is>
       </c>
-      <c r="C11" s="27" t="inlineStr">
+      <c r="C11" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">다
 아</t>
@@ -2853,7 +2876,7 @@
 汰</t>
         </is>
       </c>
-      <c r="E11" s="26" t="inlineStr">
+      <c r="E11" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">주
 우</t>
@@ -2866,7 +2889,7 @@
 姑</t>
         </is>
       </c>
-      <c r="G11" s="27" t="inlineStr">
+      <c r="G11" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">자
 아</t>
@@ -2879,7 +2902,7 @@
 汰</t>
         </is>
       </c>
-      <c r="I11" s="27" t="inlineStr">
+      <c r="I11" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">못</t>
         </is>
@@ -2892,7 +2915,7 @@
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="C12" s="22" t="inlineStr">
+      <c r="C12" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">오</t>
         </is>
@@ -2902,7 +2925,7 @@
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="E12" s="28" t="inlineStr">
+      <c r="E12" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">마</t>
         </is>
@@ -2912,7 +2935,7 @@
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="G12" s="22" t="inlineStr">
+      <c r="G12" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">야</t>
         </is>
@@ -2922,7 +2945,7 @@
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="I12" s="22" t="inlineStr">
+      <c r="I12" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
@@ -2935,26 +2958,26 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C13" s="25"/>
+      <c r="C13" s="31"/>
       <c r="D13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="E13" s="25"/>
+      <c r="E13" s="31"/>
       <c r="F13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="G13" s="25"/>
+      <c r="G13" s="31"/>
       <c r="H13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 △</t>
         </is>
       </c>
-      <c r="I13" s="25"/>
+      <c r="I13" s="31"/>
     </row>
     <row r="14" ht="87.31" customHeight="1">
       <c r="A14" s="0"/>
@@ -2963,7 +2986,7 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C14" s="26"/>
+      <c r="C14" s="32"/>
       <c r="D14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
@@ -2971,13 +2994,13 @@
 汰</t>
         </is>
       </c>
-      <c r="E14" s="27"/>
+      <c r="E14" s="33"/>
       <c r="F14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="G14" s="26"/>
+      <c r="G14" s="32"/>
       <c r="H14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
@@ -2985,7 +3008,7 @@
 汰</t>
         </is>
       </c>
-      <c r="I14" s="26"/>
+      <c r="I14" s="32"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/sheets/민요/검수/상주 모심기.xlsx
+++ b/sheets/민요/검수/상주 모심기.xlsx
@@ -11,7 +11,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="8">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <name val="궁서체"/>
@@ -42,11 +42,6 @@
     </font>
     <font>
       <sz val="24"/>
-      <name val="궁서체"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="12"/>
       <name val="궁서체"/>
       <family val="2"/>
     </font>
@@ -155,7 +150,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -241,24 +236,6 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -425,7 +402,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">손으로 그린 격자(인쇄 정간 번호 없음), 굵은 선 3칸마다로 12정간·3/4로 판독. 율명 줄 오른쪽 바깥 칸에 구간 표시 "(상주 모심기군"(4~7정간 높이), "(중모리"(7~8정간 높이)가 적혀 있음(율명 아님). 실제 내용은 오른쪽 4줄(1~4줄), 5·6줄과 그 왼쪽 인쇄 줄은 비어 있음. 1~4줄 여러 칸의 긴 물결선(요성)은 기호표에 없어 생략. 검게 스캔된 사각형은 정정 종이를 붙이고 다시 쓴 칸으로 보아 그 위에 흰 획으로 보이는 글자를 판독함. 3줄 7~12정간은 1줄 7~12정간과 같은 가락. AI 재판독.</t>
+          <t xml:space="preserve">10-13 전면 재판독. 손으로 그린 격자, 번호 없음. 12정간, 굵은 선 3칸마다 → 3/4. 내용은 오른쪽 4줄, 왼쪽 빈 줄은 뺌. 1줄 가사 칸 오른쪽 바깥에 "(상주 모심기)"(4~6정간), "(중모리)"(7~9정간) 표기(율명 아님). 여러 칸의 긴 물결선(요성)은 생략. 검은 사각형은 정정 종이를 붙여 다시 쓴 칸으로, 흰 획 글자를 판독. 1·3줄 7~12정간, 2·4줄은 같은 가락.</t>
         </is>
       </c>
     </row>
@@ -613,14 +590,13 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無|–|南</t>
+          <t xml:space="preserve">無|–南</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">無
-–
-南</t>
+–南</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -728,14 +704,13 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無|–|南</t>
+          <t xml:space="preserve">無|–南</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">無
-–
-南</t>
+–南</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1052,7 +1027,7 @@
       <c r="I13" s="3"/>
       <c r="J13" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">가운데 氵 획 흐림, 9정간과 같은 가락이라 㴌</t>
+          <t xml:space="preserve">가운데 氵 안 보여 姑일 수도, 9정간과 같은 가락으로 㴌</t>
         </is>
       </c>
       <c r="K13" s="2"/>
@@ -1389,14 +1364,13 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲|–|姑</t>
+          <t xml:space="preserve">仲|–姑</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
-–
-姑</t>
+–姑</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1636,7 +1610,7 @@
       </c>
       <c r="J28" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">정정 종이 위 글자, 汰로 보임</t>
+          <t xml:space="preserve">검은 정정 종이 위 글자, 汰로 보임</t>
         </is>
       </c>
       <c r="K28" s="2"/>
@@ -1794,7 +1768,7 @@
       </c>
       <c r="J32" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">정정 종이 위 글자</t>
+          <t xml:space="preserve">검은 정정 종이 위 글자</t>
         </is>
       </c>
       <c r="K32" s="2"/>
@@ -1838,7 +1812,7 @@
       </c>
       <c r="J33" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">정정 종이 2장 위 글자</t>
+          <t xml:space="preserve">검은 정정 종이 2장 위, 1줄 8정간과 같은 가락</t>
         </is>
       </c>
       <c r="K33" s="2"/>
@@ -1883,7 +1857,7 @@
       </c>
       <c r="J34" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">정정 종이 위 글자, 1줄 9정간과 같은 가락</t>
+          <t xml:space="preserve">검은 정정 종이 위, 1줄 9정간과 같은 가락</t>
         </is>
       </c>
       <c r="K34" s="2"/>
@@ -1926,7 +1900,7 @@
       </c>
       <c r="J35" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">정정 종이 위 글자</t>
+          <t xml:space="preserve">검은 정정 종이 위 글자</t>
         </is>
       </c>
       <c r="K35" s="2"/>
@@ -2079,7 +2053,7 @@
       <c r="I39" s="3"/>
       <c r="J39" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">정정 종이 위 글자</t>
+          <t xml:space="preserve">검은 정정 종이 위, – 아래 南으로 보임</t>
         </is>
       </c>
       <c r="K39" s="2"/>
@@ -2123,7 +2097,7 @@
       </c>
       <c r="J40" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">정정 종이 위, 위쪽 – 획이 亻일 수도(㑲?)</t>
+          <t xml:space="preserve">검은 정정 종이 위, 2줄 3정간과 같은 가락</t>
         </is>
       </c>
       <c r="K40" s="2"/>
@@ -2344,14 +2318,13 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲|–|姑</t>
+          <t xml:space="preserve">仲|–姑</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
-–
-姑</t>
+–姑</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
@@ -2470,7 +2443,7 @@
       <c r="I49" s="3"/>
       <c r="J49" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">아래 ○는 갈고리 달린 고리(∂) 모양</t>
+          <t xml:space="preserve">위 작은 갈고리 점, 아래 ○는 갈고리 달린 고리(∂) 모양</t>
         </is>
       </c>
       <c r="K49" s="2"/>
@@ -2497,7 +2470,7 @@
     <row r="1">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="87.31" customHeight="1">
+    <row r="2" ht="81.3" customHeight="1">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -2512,7 +2485,7 @@
       <c r="H2" s="20"/>
       <c r="I2" s="20"/>
     </row>
-    <row r="3" ht="87.31" customHeight="1">
+    <row r="3" ht="81.3" customHeight="1">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -2521,7 +2494,7 @@
 –</t>
         </is>
       </c>
-      <c r="C3" s="29" t="inlineStr">
+      <c r="C3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">우
 리</t>
@@ -2532,7 +2505,7 @@
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="E3" s="29" t="inlineStr">
+      <c r="E3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">여</t>
         </is>
@@ -2544,7 +2517,7 @@
 –</t>
         </is>
       </c>
-      <c r="G3" s="29" t="inlineStr">
+      <c r="G3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">여
 밥</t>
@@ -2553,17 +2526,16 @@
       <c r="H3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
-–
-南</t>
-        </is>
-      </c>
-      <c r="I3" s="29" t="inlineStr">
+–南</t>
+        </is>
+      </c>
+      <c r="I3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">상</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="87.31" customHeight="1">
+    <row r="4" ht="81.3" customHeight="1">
       <c r="A4" s="0"/>
       <c r="B4" s="23" t="inlineStr">
         <is>
@@ -2571,13 +2543,13 @@
 南</t>
         </is>
       </c>
-      <c r="C4" s="30"/>
+      <c r="C4" s="24"/>
       <c r="D4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="E4" s="31" t="inlineStr">
+      <c r="E4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">연</t>
         </is>
@@ -2587,19 +2559,19 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="G4" s="31"/>
+      <c r="G4" s="25"/>
       <c r="H4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="I4" s="31" t="inlineStr">
+      <c r="I4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">주</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="87.31" customHeight="1">
+    <row r="5" ht="81.3" customHeight="1">
       <c r="A5" s="0"/>
       <c r="B5" s="23" t="inlineStr">
         <is>
@@ -2607,7 +2579,7 @@
 南</t>
         </is>
       </c>
-      <c r="C5" s="32" t="inlineStr">
+      <c r="C5" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
@@ -2617,7 +2589,7 @@
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="E5" s="32" t="inlineStr">
+      <c r="E5" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">밥</t>
         </is>
@@ -2628,7 +2600,7 @@
 南</t>
         </is>
       </c>
-      <c r="G5" s="33" t="inlineStr">
+      <c r="G5" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">압</t>
         </is>
@@ -2638,16 +2610,16 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="I5" s="33"/>
-    </row>
-    <row r="6" ht="87.31" customHeight="1">
+      <c r="I5" s="27"/>
+    </row>
+    <row r="6" ht="81.3" customHeight="1">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="C6" s="29" t="inlineStr">
+      <c r="C6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">부</t>
         </is>
@@ -2657,7 +2629,7 @@
           <t xml:space="preserve">汰^</t>
         </is>
       </c>
-      <c r="E6" s="29" t="inlineStr">
+      <c r="E6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">줄</t>
         </is>
@@ -2667,7 +2639,7 @@
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="G6" s="29" t="inlineStr">
+      <c r="G6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">따</t>
         </is>
@@ -2675,31 +2647,30 @@
       <c r="H6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
-–
-南</t>
-        </is>
-      </c>
-      <c r="I6" s="29" t="inlineStr">
+–南</t>
+        </is>
+      </c>
+      <c r="I6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">함</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="87.31" customHeight="1">
+    <row r="7" ht="81.3" customHeight="1">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C7" s="31"/>
+      <c r="C7" s="25"/>
       <c r="D7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無南
 仲</t>
         </is>
       </c>
-      <c r="E7" s="31" t="inlineStr">
+      <c r="E7" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">바
 압</t>
@@ -2710,26 +2681,26 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="G7" s="31"/>
+      <c r="G7" s="25"/>
       <c r="H7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="I7" s="31" t="inlineStr">
+      <c r="I7" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">창</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="87.31" customHeight="1">
+    <row r="8" ht="81.3" customHeight="1">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="C8" s="33" t="inlineStr">
+      <c r="C8" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">모</t>
         </is>
@@ -2740,13 +2711,13 @@
 △</t>
         </is>
       </c>
-      <c r="E8" s="33"/>
+      <c r="E8" s="27"/>
       <c r="F8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="G8" s="33" t="inlineStr">
+      <c r="G8" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">는</t>
         </is>
@@ -2757,16 +2728,16 @@
 △</t>
         </is>
       </c>
-      <c r="I8" s="33"/>
-    </row>
-    <row r="9" ht="87.31" customHeight="1">
+      <c r="I8" s="27"/>
+    </row>
+    <row r="9" ht="81.3" customHeight="1">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="C9" s="29" t="inlineStr">
+      <c r="C9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">모</t>
         </is>
@@ -2776,7 +2747,7 @@
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="E9" s="34" t="inlineStr">
+      <c r="E9" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">내</t>
         </is>
@@ -2786,7 +2757,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="G9" s="29" t="inlineStr">
+      <c r="G9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">저</t>
         </is>
@@ -2796,13 +2767,13 @@
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="I9" s="29" t="inlineStr">
+      <c r="I9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">공</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="87.31" customHeight="1">
+    <row r="10" ht="81.3" customHeight="1">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -2811,7 +2782,7 @@
 南</t>
         </is>
       </c>
-      <c r="C10" s="31" t="inlineStr">
+      <c r="C10" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">셔
 어</t>
@@ -2823,7 +2794,7 @@
 汰</t>
         </is>
       </c>
-      <c r="E10" s="30" t="inlineStr">
+      <c r="E10" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">따
 아</t>
@@ -2836,7 +2807,7 @@
 南</t>
         </is>
       </c>
-      <c r="G10" s="31" t="inlineStr">
+      <c r="G10" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">처
 어</t>
@@ -2848,22 +2819,21 @@
 汰</t>
         </is>
       </c>
-      <c r="I10" s="31" t="inlineStr">
+      <c r="I10" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">갈</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="87.31" customHeight="1">
+    <row r="11" ht="81.3" customHeight="1">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
-–
-姑</t>
-        </is>
-      </c>
-      <c r="C11" s="33" t="inlineStr">
+–姑</t>
+        </is>
+      </c>
+      <c r="C11" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">다
 아</t>
@@ -2876,7 +2846,7 @@
 汰</t>
         </is>
       </c>
-      <c r="E11" s="32" t="inlineStr">
+      <c r="E11" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">주
 우</t>
@@ -2885,11 +2855,10 @@
       <c r="F11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
-–
-姑</t>
-        </is>
-      </c>
-      <c r="G11" s="33" t="inlineStr">
+–姑</t>
+        </is>
+      </c>
+      <c r="G11" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">자
 아</t>
@@ -2902,20 +2871,20 @@
 汰</t>
         </is>
       </c>
-      <c r="I11" s="33" t="inlineStr">
+      <c r="I11" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">못</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="87.31" customHeight="1">
+    <row r="12" ht="81.3" customHeight="1">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="C12" s="29" t="inlineStr">
+      <c r="C12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">오</t>
         </is>
@@ -2925,7 +2894,7 @@
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="E12" s="34" t="inlineStr">
+      <c r="E12" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">마</t>
         </is>
@@ -2935,7 +2904,7 @@
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="G12" s="29" t="inlineStr">
+      <c r="G12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">야</t>
         </is>
@@ -2945,48 +2914,48 @@
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="I12" s="29" t="inlineStr">
+      <c r="I12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="87.31" customHeight="1">
+    <row r="13" ht="81.3" customHeight="1">
       <c r="A13" s="0"/>
       <c r="B13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C13" s="31"/>
+      <c r="C13" s="25"/>
       <c r="D13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="E13" s="31"/>
+      <c r="E13" s="25"/>
       <c r="F13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="G13" s="31"/>
+      <c r="G13" s="25"/>
       <c r="H13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 △</t>
         </is>
       </c>
-      <c r="I13" s="31"/>
-    </row>
-    <row r="14" ht="87.31" customHeight="1">
+      <c r="I13" s="25"/>
+    </row>
+    <row r="14" ht="81.3" customHeight="1">
       <c r="A14" s="0"/>
       <c r="B14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C14" s="32"/>
+      <c r="C14" s="26"/>
       <c r="D14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
@@ -2994,13 +2963,13 @@
 汰</t>
         </is>
       </c>
-      <c r="E14" s="33"/>
+      <c r="E14" s="27"/>
       <c r="F14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="G14" s="32"/>
+      <c r="G14" s="26"/>
       <c r="H14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
@@ -3008,7 +2977,7 @@
 汰</t>
         </is>
       </c>
-      <c r="I14" s="32"/>
+      <c r="I14" s="26"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/sheets/민요/검수/상주 모심기.xlsx
+++ b/sheets/민요/검수/상주 모심기.xlsx
@@ -509,10 +509,7 @@
       </patternFill>
     </fill>
     <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFF2CC"/>
-        <bgColor rgb="FFFFFFFF"/>
-      </patternFill>
+      <patternFill patternType="none"/>
     </fill>
   </fills>
   <borders count="5">

--- a/sheets/민요/검수/상주 모심기.xlsx
+++ b/sheets/민요/검수/상주 모심기.xlsx
@@ -414,24 +414,8 @@
 아</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="24"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">–
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="24"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">△</t>
-    </r>
+    <t xml:space="preserve">–
+△</t>
   </si>
 </sst>
 </file>
@@ -450,17 +434,17 @@
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="궁서체"/>
       <family val="0"/>
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="궁서체"/>
       <family val="0"/>
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="궁서체"/>
       <family val="0"/>
     </font>
     <font>
@@ -582,7 +566,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="26">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -640,6 +624,50 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="3" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="4" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2580,316 +2608,316 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
+    <pageSetUpPr fitToPage="0"/>
   </sheetPr>
   <dimension ref="B1:I14"/>
   <sheetFormatPr defaultColWidth="8.5078125" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="16" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="16" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="16" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="16" width="6"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="2" customFormat="false" ht="81.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="6" t="s">
+    <row r="1" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="6.0" customHeight="true"/>
+    <row r="2" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="64.52" customHeight="true">
+      <c r="B2" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="6"/>
-      <c r="G2" s="6"/>
-      <c r="H2" s="6"/>
-      <c r="I2" s="6"/>
-    </row>
-    <row r="3" customFormat="false" ht="81.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B3" s="7" t="s">
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
+      <c r="G2" s="17"/>
+      <c r="H2" s="17"/>
+      <c r="I2" s="17"/>
+    </row>
+    <row r="3" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="96.05" customHeight="true">
+      <c r="B3" s="18" t="s">
         <v>67</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="19" t="s">
         <v>113</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D3" s="18" t="s">
         <v>84</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="E3" s="19" t="s">
         <v>85</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="F3" s="18" t="s">
         <v>67</v>
       </c>
-      <c r="G3" s="8" t="s">
+      <c r="G3" s="19" t="s">
         <v>114</v>
       </c>
-      <c r="H3" s="7" t="s">
+      <c r="H3" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="I3" s="8" t="s">
+      <c r="I3" s="19" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="81.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="9" t="s">
+    <row r="4" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="96.05" customHeight="true">
+      <c r="B4" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="C4" s="10"/>
-      <c r="D4" s="7" t="s">
+      <c r="C4" s="21"/>
+      <c r="D4" s="18" t="s">
         <v>86</v>
       </c>
-      <c r="E4" s="11" t="s">
+      <c r="E4" s="22" t="s">
         <v>87</v>
       </c>
-      <c r="F4" s="7" t="s">
+      <c r="F4" s="18" t="s">
         <v>51</v>
       </c>
-      <c r="G4" s="11"/>
-      <c r="H4" s="7" t="s">
+      <c r="G4" s="22"/>
+      <c r="H4" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="I4" s="11" t="s">
+      <c r="I4" s="22" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="81.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="9" t="s">
+    <row r="5" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="96.05" customHeight="true">
+      <c r="B5" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="C5" s="12" t="s">
+      <c r="C5" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="D5" s="9" t="s">
+      <c r="D5" s="20" t="s">
         <v>88</v>
       </c>
-      <c r="E5" s="12" t="s">
+      <c r="E5" s="23" t="s">
         <v>89</v>
       </c>
-      <c r="F5" s="7" t="s">
+      <c r="F5" s="18" t="s">
         <v>70</v>
       </c>
-      <c r="G5" s="13" t="s">
+      <c r="G5" s="24" t="s">
         <v>71</v>
       </c>
-      <c r="H5" s="7" t="s">
+      <c r="H5" s="18" t="s">
         <v>51</v>
       </c>
-      <c r="I5" s="13"/>
-    </row>
-    <row r="6" customFormat="false" ht="81.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="7" t="s">
+      <c r="I5" s="24"/>
+    </row>
+    <row r="6" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="96.05" customHeight="true">
+      <c r="B6" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="C6" s="19" t="s">
         <v>106</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="D6" s="18" t="s">
         <v>91</v>
       </c>
-      <c r="E6" s="8" t="s">
+      <c r="E6" s="19" t="s">
         <v>37</v>
       </c>
-      <c r="F6" s="7" t="s">
+      <c r="F6" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="G6" s="8" t="s">
+      <c r="G6" s="19" t="s">
         <v>72</v>
       </c>
-      <c r="H6" s="7" t="s">
+      <c r="H6" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="I6" s="8" t="s">
+      <c r="I6" s="19" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="81.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="7" t="s">
+    <row r="7" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="96.05" customHeight="true">
+      <c r="B7" s="18" t="s">
         <v>51</v>
       </c>
-      <c r="C7" s="11"/>
-      <c r="D7" s="7" t="s">
+      <c r="C7" s="22"/>
+      <c r="D7" s="18" t="s">
         <v>93</v>
       </c>
-      <c r="E7" s="11" t="s">
+      <c r="E7" s="22" t="s">
         <v>115</v>
       </c>
-      <c r="F7" s="7" t="s">
+      <c r="F7" s="18" t="s">
         <v>51</v>
       </c>
-      <c r="G7" s="11"/>
-      <c r="H7" s="7" t="s">
+      <c r="G7" s="22"/>
+      <c r="H7" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="I7" s="11" t="s">
+      <c r="I7" s="22" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="81.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="7" t="s">
+    <row r="8" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="96.05" customHeight="true">
+      <c r="B8" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="C8" s="13" t="s">
+      <c r="C8" s="24" t="s">
         <v>107</v>
       </c>
-      <c r="D8" s="7" t="s">
+      <c r="D8" s="18" t="s">
         <v>55</v>
       </c>
-      <c r="E8" s="13"/>
-      <c r="F8" s="7" t="s">
+      <c r="E8" s="24"/>
+      <c r="F8" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="G8" s="13" t="s">
+      <c r="G8" s="24" t="s">
         <v>73</v>
       </c>
-      <c r="H8" s="7" t="s">
+      <c r="H8" s="18" t="s">
         <v>55</v>
       </c>
-      <c r="I8" s="13"/>
-    </row>
-    <row r="9" customFormat="false" ht="81.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="7" t="s">
+      <c r="I8" s="24"/>
+    </row>
+    <row r="9" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="96.05" customHeight="true">
+      <c r="B9" s="18" t="s">
         <v>74</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="19" t="s">
         <v>107</v>
       </c>
-      <c r="D9" s="9" t="s">
+      <c r="D9" s="20" t="s">
         <v>56</v>
       </c>
-      <c r="E9" s="14" t="s">
+      <c r="E9" s="25" t="s">
         <v>95</v>
       </c>
-      <c r="F9" s="7" t="s">
+      <c r="F9" s="18" t="s">
         <v>74</v>
       </c>
-      <c r="G9" s="8" t="s">
+      <c r="G9" s="19" t="s">
         <v>75</v>
       </c>
-      <c r="H9" s="7" t="s">
+      <c r="H9" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="I9" s="8" t="s">
+      <c r="I9" s="19" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="81.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="7" t="s">
+    <row r="10" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="96.05" customHeight="true">
+      <c r="B10" s="18" t="s">
         <v>77</v>
       </c>
-      <c r="C10" s="11" t="s">
+      <c r="C10" s="22" t="s">
         <v>116</v>
       </c>
-      <c r="D10" s="9" t="s">
+      <c r="D10" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="E10" s="10" t="s">
+      <c r="E10" s="21" t="s">
         <v>117</v>
       </c>
-      <c r="F10" s="7" t="s">
+      <c r="F10" s="18" t="s">
         <v>77</v>
       </c>
-      <c r="G10" s="11" t="s">
+      <c r="G10" s="22" t="s">
         <v>118</v>
       </c>
-      <c r="H10" s="7" t="s">
+      <c r="H10" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="I10" s="11" t="s">
+      <c r="I10" s="22" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="81.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="7" t="s">
+    <row r="11" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="96.05" customHeight="true">
+      <c r="B11" s="18" t="s">
         <v>80</v>
       </c>
-      <c r="C11" s="13" t="s">
+      <c r="C11" s="24" t="s">
         <v>119</v>
       </c>
-      <c r="D11" s="9" t="s">
+      <c r="D11" s="20" t="s">
         <v>62</v>
       </c>
-      <c r="E11" s="12" t="s">
+      <c r="E11" s="23" t="s">
         <v>120</v>
       </c>
-      <c r="F11" s="7" t="s">
+      <c r="F11" s="18" t="s">
         <v>80</v>
       </c>
-      <c r="G11" s="13" t="s">
+      <c r="G11" s="24" t="s">
         <v>121</v>
       </c>
-      <c r="H11" s="7" t="s">
+      <c r="H11" s="18" t="s">
         <v>62</v>
       </c>
-      <c r="I11" s="13" t="s">
+      <c r="I11" s="24" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="81.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="7" t="s">
+    <row r="12" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="96.05" customHeight="true">
+      <c r="B12" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="C12" s="8" t="s">
+      <c r="C12" s="19" t="s">
         <v>110</v>
       </c>
-      <c r="D12" s="9" t="s">
+      <c r="D12" s="20" t="s">
         <v>56</v>
       </c>
-      <c r="E12" s="14" t="s">
+      <c r="E12" s="25" t="s">
         <v>101</v>
       </c>
-      <c r="F12" s="7" t="s">
+      <c r="F12" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="G12" s="8" t="s">
+      <c r="G12" s="19" t="s">
         <v>82</v>
       </c>
-      <c r="H12" s="7" t="s">
+      <c r="H12" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="I12" s="8" t="s">
+      <c r="I12" s="19" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="81.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="7" t="s">
+    <row r="13" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="96.05" customHeight="true">
+      <c r="B13" s="18" t="s">
         <v>51</v>
       </c>
-      <c r="C13" s="11"/>
-      <c r="D13" s="7" t="s">
+      <c r="C13" s="22"/>
+      <c r="D13" s="18" t="s">
         <v>51</v>
       </c>
-      <c r="E13" s="11"/>
-      <c r="F13" s="7" t="s">
+      <c r="E13" s="22"/>
+      <c r="F13" s="18" t="s">
         <v>51</v>
       </c>
-      <c r="G13" s="11"/>
-      <c r="H13" s="7" t="s">
+      <c r="G13" s="22"/>
+      <c r="H13" s="18" t="s">
         <v>55</v>
       </c>
-      <c r="I13" s="11"/>
-    </row>
-    <row r="14" customFormat="false" ht="81.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="9" t="s">
+      <c r="I13" s="22"/>
+    </row>
+    <row r="14" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="96.05" customHeight="true">
+      <c r="B14" s="20" t="s">
         <v>122</v>
       </c>
-      <c r="C14" s="12"/>
-      <c r="D14" s="7" t="s">
+      <c r="C14" s="23"/>
+      <c r="D14" s="18" t="s">
         <v>62</v>
       </c>
-      <c r="E14" s="13"/>
-      <c r="F14" s="9" t="s">
+      <c r="E14" s="24"/>
+      <c r="F14" s="20" t="s">
         <v>122</v>
       </c>
-      <c r="G14" s="12"/>
-      <c r="H14" s="9" t="s">
+      <c r="G14" s="23"/>
+      <c r="H14" s="20" t="s">
         <v>62</v>
       </c>
-      <c r="I14" s="12"/>
+      <c r="I14" s="23"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2897,7 +2925,7 @@
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="true" verticalCentered="false"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="62"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>

--- a/sheets/민요/검수/상주 모심기.xlsx
+++ b/sheets/민요/검수/상주 모심기.xlsx
@@ -2614,13 +2614,13 @@
   <sheetFormatPr defaultColWidth="8.5078125" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="15" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="16" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="15" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="16" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="15" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="16" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="15" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="16" width="6"/>
   </cols>
   <sheetData>
